--- a/LoanOfficer-A/2026/172 Mutum sandhyarani.xlsx
+++ b/LoanOfficer-A/2026/172 Mutum sandhyarani.xlsx
@@ -807,7 +807,7 @@
       </c>
       <c r="K1" s="10">
         <f>G1-K2</f>
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="L1" s="6"/>
       <c r="M1" s="5"/>
@@ -816,7 +816,7 @@
       </c>
       <c r="O1" s="8">
         <f>SUM(C3:C32)+SUM(G3:G32)+SUM(K3:K32)+SUM(O3:O32)</f>
-        <v>3500</v>
+        <v>4900</v>
       </c>
       <c r="P1" s="6"/>
     </row>
@@ -845,7 +845,7 @@
       </c>
       <c r="K2" s="9">
         <f>SUM(D3:D32)+SUM(H3:H32)+SUM(L3:L32)+SUM(P3:P32)</f>
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="L2" s="6"/>
       <c r="M2" s="5"/>
@@ -854,7 +854,7 @@
       </c>
       <c r="O2" s="11">
         <f>C2-O1</f>
-        <v>8400</v>
+        <v>7000</v>
       </c>
       <c r="P2" s="6"/>
     </row>
@@ -1022,9 +1022,15 @@
       <c r="A8" s="1">
         <v>6</v>
       </c>
-      <c r="B8" s="3"/>
-      <c r="C8" s="4"/>
-      <c r="D8" s="1"/>
+      <c r="B8" s="3">
+        <v>46171</v>
+      </c>
+      <c r="C8" s="4">
+        <v>700</v>
+      </c>
+      <c r="D8" s="1">
+        <v>1</v>
+      </c>
       <c r="E8" s="1">
         <v>36</v>
       </c>
@@ -1048,9 +1054,15 @@
       <c r="A9" s="1">
         <v>7</v>
       </c>
-      <c r="B9" s="3"/>
-      <c r="C9" s="4"/>
-      <c r="D9" s="1"/>
+      <c r="B9" s="3">
+        <v>46171</v>
+      </c>
+      <c r="C9" s="4">
+        <v>700</v>
+      </c>
+      <c r="D9" s="1">
+        <v>1</v>
+      </c>
       <c r="E9" s="1">
         <v>37</v>
       </c>
